--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_391_R42.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_391_R42.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9639</v>
+        <v>6.0878</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2897</v>
+        <v>4.4783</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6742</v>
+        <v>1.6096</v>
       </c>
       <c r="G2" t="n">
         <v>2.9239</v>
@@ -610,13 +610,13 @@
         <v>2.2747</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2202</v>
+        <v>0.3441</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2273</v>
+        <v>-0.0388</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4476</v>
+        <v>0.3829</v>
       </c>
       <c r="V2" t="n">
         <v>0.5451</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7407</v>
+        <v>5.5255</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5386</v>
+        <v>5.1941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2021</v>
+        <v>0.3314</v>
       </c>
       <c r="G3" t="n">
         <v>3.5581</v>
@@ -688,13 +688,13 @@
         <v>0.9099</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2251</v>
+        <v>0.5597</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8619</v>
+        <v>-0.2064</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6368</v>
+        <v>0.7661</v>
       </c>
       <c r="V3" t="n">
         <v>1.6352</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5742</v>
+        <v>5.3016</v>
       </c>
       <c r="E4" t="n">
-        <v>6.483</v>
+        <v>7.2103</v>
       </c>
       <c r="F4" t="n">
         <v>-1.9087</v>
@@ -766,10 +766,10 @@
         <v>2.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.1946</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0056</v>
+        <v>-0.2782</v>
       </c>
       <c r="U4" t="n">
         <v>0.0837</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.541</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6929</v>
+        <v>1.0866</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2339</v>
+        <v>-0.2897</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1256</v>
+        <v>0.5485</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5686</v>
+        <v>0.6909</v>
       </c>
       <c r="I5" t="n">
-        <v>0.443</v>
+        <v>-0.1424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1593</v>
+        <v>2.0892</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.623</v>
+        <v>0.8971</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7823</v>
+        <v>1.1921</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.285</v>
+        <v>-1.5407</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0544</v>
+        <v>-0.2063</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3393</v>
+        <v>-1.3345</v>
       </c>
       <c r="P5" t="n">
         <v>-0.2275</v>
@@ -844,28 +844,28 @@
         <v>0.9099</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6675</v>
+        <v>0.4759</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8319</v>
+        <v>0.1347</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8356</v>
+        <v>0.3412</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.5468</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.673</v>
+        <v>0.3162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7364000000000001</v>
+        <v>-1.7884</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0634</v>
+        <v>2.1046</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5485</v>
+        <v>-0.1256</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6909</v>
+        <v>-0.5686</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1424</v>
+        <v>0.443</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0892</v>
+        <v>0.1593</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8971</v>
+        <v>-0.623</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1921</v>
+        <v>0.7823</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5407</v>
+        <v>-0.285</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2063</v>
+        <v>0.0544</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3345</v>
+        <v>-0.3393</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2275</v>
@@ -922,28 +922,28 @@
         <v>0.9099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3519</v>
+        <v>1.4427</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2155</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5674</v>
+        <v>0.7063</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.5468</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8638</v>
+        <v>-0.6765</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8978</v>
+        <v>0.9077</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7615</v>
+        <v>-1.5842</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0042</v>
+        <v>0.9742</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3634</v>
+        <v>1.9173</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3676</v>
+        <v>-0.9431</v>
       </c>
       <c r="J7" t="n">
-        <v>1.071</v>
+        <v>1.5092</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1042</v>
+        <v>2.0186</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0332</v>
+        <v>-0.5093</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0752</v>
+        <v>-0.535</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7407</v>
+        <v>-0.1013</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3345</v>
+        <v>-0.4338</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2275</v>
+        <v>1.3648</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5053</v>
+        <v>0.8471</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4191</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0862</v>
+        <v>0.3112</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5451</v>
+        <v>-2.7253</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.7253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9297</v>
+        <v>-0.7794</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7191</v>
+        <v>0.8529</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6489</v>
+        <v>-1.6323</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9742</v>
+        <v>-1.0042</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9173</v>
+        <v>0.3634</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9431</v>
+        <v>-1.3676</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5092</v>
+        <v>1.071</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0186</v>
+        <v>1.1042</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5093</v>
+        <v>-0.0332</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.535</v>
+        <v>-2.0752</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1013</v>
+        <v>-0.7407</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4338</v>
+        <v>-1.3345</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2275</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3648</v>
+        <v>0.2275</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5939</v>
+        <v>0.5897</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3473</v>
+        <v>0.3742</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2466</v>
+        <v>0.2155</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7253</v>
+        <v>0.5451</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0899</v>
+        <v>-1.0859</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1202</v>
+        <v>-0.2328</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2101</v>
+        <v>-0.8531</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5766</v>
+        <v>-0.8525</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1046</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4719</v>
+        <v>-0.1796</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9137</v>
+        <v>0.0545</v>
       </c>
       <c r="K9" t="n">
-        <v>0.788</v>
+        <v>0.0173</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1257</v>
+        <v>0.0373</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.4903</v>
+        <v>-0.907</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8927</v>
+        <v>-0.6901</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.5977</v>
+        <v>-0.2169</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6824</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8198</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.736</v>
+        <v>-0.2334</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1855</v>
+        <v>-0.2873</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5505</v>
+        <v>0.0539</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1182</v>
+        <v>-1.4605</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2328</v>
+        <v>-0.9762</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8854</v>
+        <v>-0.4843</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8525</v>
+        <v>-1.2474</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0859</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1796</v>
+        <v>-1.1615</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0545</v>
+        <v>-0.8236</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>-0.1571</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>-0.6665</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.907</v>
+        <v>-0.4237</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6901</v>
+        <v>0.0713</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2169</v>
+        <v>-0.495</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9099</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.9099</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2658</v>
+        <v>-0.0329</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2873</v>
+        <v>-0.1526</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0215</v>
+        <v>0.1197</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0693</v>
+        <v>-2.1136</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3264</v>
+        <v>1.2582</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7429</v>
+        <v>-3.3717</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2474</v>
+        <v>-2.5766</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0859</v>
+        <v>-0.1046</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1615</v>
+        <v>-2.4719</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8236</v>
+        <v>1.9137</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1571</v>
+        <v>0.788</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6665</v>
+        <v>1.1257</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4237</v>
+        <v>-4.4903</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0713</v>
+        <v>-0.8927</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.495</v>
+        <v>-3.5977</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9099</v>
+        <v>0.6824</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9099</v>
+        <v>1.8198</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6417</v>
+        <v>0.7124</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5028</v>
+        <v>0.3234</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1389</v>
+        <v>0.3889</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0901</v>
+        <v>-0.9318</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X11" t="n">
         <v>-1.0901</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6933</v>
+        <v>-5.6934</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.353</v>
+        <v>-2.5146</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3404</v>
+        <v>-3.1787</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7595</v>
@@ -1393,10 +1393,10 @@
         <v>-0.4789</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.6763</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0358</v>
+        <v>0.1974</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5451</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4727</v>
+        <v>-6.2446</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2106</v>
+        <v>-1.7886</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.262</v>
+        <v>-4.456</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3284</v>
@@ -1468,13 +1468,13 @@
         <v>0.9099</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8477</v>
+        <v>-0.6196</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0056</v>
+        <v>-0.5835</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1579</v>
+        <v>-0.0361</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9318</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7440999999999987</v>
+        <v>-0.0259000000000027</v>
       </c>
       <c r="E14" t="n">
-        <v>12.9691</v>
+        <v>13.6875</v>
       </c>
       <c r="F14" t="n">
         <v>-13.7131</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7782999999999984</v>
+        <v>-0.7783000000000011</v>
       </c>
       <c r="H14" t="n">
-        <v>5.447599999999999</v>
+        <v>5.4476</v>
       </c>
       <c r="I14" t="n">
         <v>-6.2257</v>
       </c>
       <c r="J14" t="n">
-        <v>23.09820000000001</v>
+        <v>23.0982</v>
       </c>
       <c r="K14" t="n">
         <v>10.4174</v>
@@ -1546,10 +1546,10 @@
         <v>13.6484</v>
       </c>
       <c r="S14" t="n">
-        <v>2.693700000000001</v>
+        <v>3.412199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8368000000000001</v>
+        <v>-0.1186</v>
       </c>
       <c r="U14" t="n">
         <v>3.5307</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5149</v>
+        <v>3.9761</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6003</v>
+        <v>4.8999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0854</v>
+        <v>-0.9238</v>
       </c>
       <c r="G15" t="n">
         <v>0.1072</v>
@@ -1624,13 +1624,13 @@
         <v>1.5923</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6825</v>
+        <v>0.1437</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5151</v>
+        <v>-0.1853</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1674</v>
+        <v>0.329</v>
       </c>
       <c r="V15" t="n">
         <v>3.2703</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8345</v>
+        <v>3.5059</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1683</v>
+        <v>4.5185</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3338</v>
+        <v>-1.0126</v>
       </c>
       <c r="G16" t="n">
         <v>1.6407</v>
@@ -1702,13 +1702,13 @@
         <v>1.5923</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.3202</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9816</v>
+        <v>-0.6314</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6303</v>
+        <v>0.9516</v>
       </c>
       <c r="V16" t="n">
         <v>1.0901</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.79</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>0.5548</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2352</v>
+        <v>0.1706</v>
       </c>
       <c r="G17" t="n">
         <v>0.4704</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1317</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0718</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0047</v>
+        <v>-0.0599</v>
       </c>
       <c r="V17" t="n">
         <v>0.3867</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3981</v>
+        <v>0.6089</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2035</v>
+        <v>2.4836</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1945</v>
+        <v>-1.8747</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4471</v>
+        <v>0.8258</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1729</v>
+        <v>2.2241</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.62</v>
+        <v>-1.3983</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2035</v>
+        <v>4.7099</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>3.8781</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1863</v>
+        <v>0.8318</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6506</v>
+        <v>-3.884</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1556</v>
+        <v>-1.654</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8063</v>
+        <v>-2.23</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4549</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4549</v>
+        <v>1.8198</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3902</v>
+        <v>-0.3771</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4966</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3902</v>
+        <v>0.1196</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6151</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3899</v>
+        <v>0.5725</v>
       </c>
       <c r="E19" t="n">
-        <v>2.717</v>
+        <v>2.8432</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3272</v>
+        <v>-2.2707</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8258</v>
+        <v>2.3306</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2241</v>
+        <v>0.9324</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3983</v>
+        <v>1.3983</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7099</v>
+        <v>4.4682</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8781</v>
+        <v>1.7407</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8318</v>
+        <v>2.7276</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.884</v>
+        <v>-2.1376</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.654</v>
+        <v>-0.8083</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.23</v>
+        <v>-1.3293</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4549</v>
+        <v>0.6824</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R19" t="n">
         <v>1.8198</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5961</v>
+        <v>-0.2604</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2632</v>
+        <v>-0.4877</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3329</v>
+        <v>0.2273</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6151</v>
+        <v>-2.1802</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.093</v>
+        <v>0.1395</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4929</v>
+        <v>0.2035</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4</v>
+        <v>-0.064</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3306</v>
+        <v>-0.4471</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9324</v>
+        <v>0.1729</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3983</v>
+        <v>-0.62</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4682</v>
+        <v>0.2035</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7407</v>
+        <v>0.0173</v>
       </c>
       <c r="L20" t="n">
-        <v>2.7276</v>
+        <v>0.1863</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1376</v>
+        <v>-0.6506</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8083</v>
+        <v>0.1556</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3293</v>
+        <v>-0.8063</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6824</v>
+        <v>0.4549</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8198</v>
+        <v>0.4549</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7399</v>
+        <v>0.1317</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8379</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.098</v>
+        <v>0.1317</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1802</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0037</v>
+        <v>0.113</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3812</v>
+        <v>1.498</v>
       </c>
       <c r="F21" t="n">
         <v>-1.385</v>
@@ -2092,10 +2092,10 @@
         <v>1.1374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8381</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.419</v>
+        <v>-0.3022</v>
       </c>
       <c r="U21" t="n">
         <v>-0.4191</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0556</v>
+        <v>0.0611</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3651</v>
+        <v>1.4818</v>
       </c>
       <c r="F22" t="n">
         <v>-1.4207</v>
@@ -2170,10 +2170,10 @@
         <v>1.5923</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5268</v>
+        <v>-0.41</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5626</v>
+        <v>-0.4459</v>
       </c>
       <c r="U22" t="n">
         <v>0.0358</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1337</v>
+        <v>-1.9721</v>
       </c>
       <c r="E23" t="n">
         <v>-1.2093</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9244</v>
+        <v>-0.7628</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2633</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5747</v>
+        <v>-0.4131</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2155</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3592</v>
+        <v>-0.1976</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1583</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1539</v>
+        <v>-2.7786</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4752</v>
+        <v>-0.3584</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6787</v>
+        <v>-2.4202</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6086</v>
@@ -2326,13 +2326,13 @@
         <v>0.6824</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1805</v>
+        <v>-0.8052</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4908</v>
+        <v>-0.3741</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6897</v>
+        <v>-0.4311</v>
       </c>
       <c r="V24" t="n">
         <v>1.0901</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9293</v>
+        <v>-4.2076</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9254</v>
+        <v>-2.0422</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0038</v>
+        <v>-2.1654</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9897</v>
@@ -2404,13 +2404,13 @@
         <v>1.8198</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1077</v>
+        <v>-0.1706</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2033</v>
+        <v>-0.3201</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3111</v>
+        <v>0.1495</v>
       </c>
       <c r="V25" t="n">
         <v>0.5451</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7441999999999998</v>
+        <v>0.7440000000000007</v>
       </c>
       <c r="E26" t="n">
-        <v>14.8732</v>
+        <v>14.8734</v>
       </c>
       <c r="F26" t="n">
         <v>-14.1293</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7783000000000007</v>
+        <v>0.7782999999999998</v>
       </c>
       <c r="H26" t="n">
         <v>-5.447600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>12.511</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6941</v>
+        <v>-2.6938</v>
       </c>
       <c r="T26" t="n">
         <v>-3.5306</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8366000000000002</v>
+        <v>0.8368</v>
       </c>
       <c r="V26" t="n">
         <v>3.7971</v>
